--- a/matlab/talkdata.xlsx
+++ b/matlab/talkdata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdavenport/Documents/Other/website/matlab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FF57A3-B1D7-DC47-97D8-3A5AA5430037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003BBAE7-994A-7B43-99BC-B15BC4C14F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="127">
   <si>
     <t>title</t>
   </si>
@@ -397,6 +397,15 @@
   </si>
   <si>
     <t>Big Data Institute</t>
+  </si>
+  <si>
+    <t>UCSD</t>
+  </si>
+  <si>
+    <t>llms</t>
+  </si>
+  <si>
+    <t>Using Large Language Models for research</t>
   </si>
 </sst>
 </file>
@@ -774,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.1640625" customWidth="1"/>
@@ -2223,6 +2232,47 @@
         <v>18</v>
       </c>
     </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D36" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" t="s">
+        <v>124</v>
+      </c>
+      <c r="F36" t="s">
+        <v>63</v>
+      </c>
+      <c r="G36" t="s">
+        <v>125</v>
+      </c>
+      <c r="H36" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" t="s">
+        <v>18</v>
+      </c>
+      <c r="K36" t="s">
+        <v>18</v>
+      </c>
+      <c r="L36" t="s">
+        <v>18</v>
+      </c>
+      <c r="M36" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="L26" r:id="rId1" xr:uid="{F2792CC9-C75F-4E31-9A12-D700753B1C12}"/>
